--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125570015</v>
+        <v>125568836</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>91131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,43 +1635,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604077</v>
+        <v>603952</v>
       </c>
       <c r="R11" t="n">
-        <v>6936714</v>
+        <v>6936705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,17 +1704,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125568836</v>
+        <v>125568231</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1745,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603952</v>
+        <v>603930</v>
       </c>
       <c r="R12" t="n">
-        <v>6936705</v>
+        <v>6936683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125568231</v>
+        <v>125570015</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,34 +1847,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603930</v>
+        <v>604077</v>
       </c>
       <c r="R13" t="n">
-        <v>6936683</v>
+        <v>6936714</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1912,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2245,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570268</v>
+        <v>125568069</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,34 +2265,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603962</v>
+        <v>603923</v>
       </c>
       <c r="R17" t="n">
-        <v>6936624</v>
+        <v>6936700</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,6 +2330,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125568069</v>
+        <v>125570268</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,39 +2377,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603923</v>
+        <v>603962</v>
       </c>
       <c r="R18" t="n">
-        <v>6936700</v>
+        <v>6936624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,11 +2437,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125566395</v>
+        <v>125569837</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,39 +2479,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603942</v>
+        <v>604041</v>
       </c>
       <c r="R19" t="n">
-        <v>6936844</v>
+        <v>6936707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2539,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125569837</v>
+        <v>125566395</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,34 +2581,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604041</v>
+        <v>603942</v>
       </c>
       <c r="R20" t="n">
-        <v>6936707</v>
+        <v>6936844</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2646,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125569639</v>
+        <v>125568069</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603993</v>
+        <v>603923</v>
       </c>
       <c r="R2" t="n">
-        <v>6936737</v>
+        <v>6936700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569912</v>
+        <v>125566395</v>
       </c>
       <c r="B3" t="n">
         <v>57635</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604067</v>
+        <v>603942</v>
       </c>
       <c r="R3" t="n">
-        <v>6936731</v>
+        <v>6936844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569656</v>
+        <v>125569123</v>
       </c>
       <c r="B4" t="n">
-        <v>97147</v>
+        <v>91459</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604000</v>
+        <v>603952</v>
       </c>
       <c r="R4" t="n">
-        <v>6936712</v>
+        <v>6936705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125570129</v>
+        <v>125569639</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604001</v>
+        <v>603993</v>
       </c>
       <c r="R5" t="n">
-        <v>6936685</v>
+        <v>6936737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569404</v>
+        <v>125568990</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,29 +1129,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125568260</v>
+        <v>125570230</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,34 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603930</v>
+        <v>603979</v>
       </c>
       <c r="R7" t="n">
-        <v>6936683</v>
+        <v>6936633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570366</v>
+        <v>125570129</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,34 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603906</v>
+        <v>604001</v>
       </c>
       <c r="R8" t="n">
-        <v>6936672</v>
+        <v>6936685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125570219</v>
+        <v>125569656</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>97147</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,43 +1431,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604001</v>
+        <v>604000</v>
       </c>
       <c r="R9" t="n">
-        <v>6936685</v>
+        <v>6936712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125568990</v>
+        <v>125569404</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,24 +1537,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1729,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125568231</v>
+        <v>125569588</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,34 +1750,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603930</v>
+        <v>603975</v>
       </c>
       <c r="R12" t="n">
-        <v>6936683</v>
+        <v>6936747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125569588</v>
+        <v>125570366</v>
       </c>
       <c r="B14" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,34 +1964,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603975</v>
+        <v>603906</v>
       </c>
       <c r="R14" t="n">
-        <v>6936747</v>
+        <v>6936672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125570230</v>
+        <v>125570268</v>
       </c>
       <c r="B15" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2090,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603979</v>
+        <v>603962</v>
       </c>
       <c r="R15" t="n">
-        <v>6936633</v>
+        <v>6936624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569123</v>
+        <v>125569912</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,34 +2168,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603952</v>
+        <v>604067</v>
       </c>
       <c r="R16" t="n">
-        <v>6936705</v>
+        <v>6936731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,6 +2233,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125568069</v>
+        <v>125569837</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,39 +2280,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603923</v>
+        <v>604041</v>
       </c>
       <c r="R17" t="n">
-        <v>6936700</v>
+        <v>6936707</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,11 +2340,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125570268</v>
+        <v>125568260</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,34 +2382,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603962</v>
+        <v>603930</v>
       </c>
       <c r="R18" t="n">
-        <v>6936624</v>
+        <v>6936683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,7 +2468,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125569837</v>
+        <v>125568231</v>
       </c>
       <c r="B19" t="n">
         <v>80028</v>
@@ -2499,14 +2504,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604041</v>
+        <v>603930</v>
       </c>
       <c r="R19" t="n">
-        <v>6936707</v>
+        <v>6936683</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125566395</v>
+        <v>125570219</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2581,16 +2586,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2610,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603942</v>
+        <v>604001</v>
       </c>
       <c r="R20" t="n">
-        <v>6936844</v>
+        <v>6936685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,11 +2651,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125568069</v>
+        <v>125568260</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603923</v>
+        <v>603930</v>
       </c>
       <c r="R2" t="n">
-        <v>6936700</v>
+        <v>6936683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125566395</v>
+        <v>125568836</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603942</v>
+        <v>603952</v>
       </c>
       <c r="R3" t="n">
-        <v>6936844</v>
+        <v>6936705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,17 +848,13 @@
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569123</v>
+        <v>125569588</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603952</v>
+        <v>603975</v>
       </c>
       <c r="R4" t="n">
-        <v>6936705</v>
+        <v>6936747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125569639</v>
+        <v>125568990</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603993</v>
+        <v>603964</v>
       </c>
       <c r="R5" t="n">
-        <v>6936737</v>
+        <v>6936709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125568990</v>
+        <v>125569404</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,24 +1078,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1215,15 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125570230</v>
+        <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603979</v>
+        <v>604001</v>
       </c>
       <c r="R7" t="n">
-        <v>6936633</v>
+        <v>6936685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570129</v>
+        <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1277,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604001</v>
+        <v>603906</v>
       </c>
       <c r="R8" t="n">
-        <v>6936685</v>
+        <v>6936672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,50 +1363,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125569656</v>
+        <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604000</v>
+        <v>604067</v>
       </c>
       <c r="R9" t="n">
-        <v>6936712</v>
+        <v>6936731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,15 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125569404</v>
+        <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,39 +1481,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R10" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,53 +1567,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125568836</v>
+        <v>125570230</v>
       </c>
       <c r="B11" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603952</v>
+        <v>603979</v>
       </c>
       <c r="R11" t="n">
-        <v>6936705</v>
+        <v>6936633</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1646,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1734,15 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125569588</v>
+        <v>125568069</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,34 +1675,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603975</v>
+        <v>603923</v>
       </c>
       <c r="R12" t="n">
-        <v>6936747</v>
+        <v>6936700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,6 +1740,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,15 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125570015</v>
+        <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,16 +1782,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1872,7 +1802,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1881,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604077</v>
+        <v>604001</v>
       </c>
       <c r="R13" t="n">
-        <v>6936714</v>
+        <v>6936685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,11 +1847,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,15 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125570366</v>
+        <v>125566395</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,34 +1884,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603906</v>
+        <v>603942</v>
       </c>
       <c r="R14" t="n">
-        <v>6936672</v>
+        <v>6936844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,6 +1949,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2050,37 +1980,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125570268</v>
+        <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603962</v>
+        <v>604000</v>
       </c>
       <c r="R15" t="n">
-        <v>6936624</v>
+        <v>6936712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,15 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569912</v>
+        <v>125570015</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2108,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2197,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604067</v>
+        <v>604077</v>
       </c>
       <c r="R16" t="n">
-        <v>6936731</v>
+        <v>6936714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2157,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,15 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569837</v>
+        <v>125569639</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,34 +2195,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604041</v>
+        <v>603993</v>
       </c>
       <c r="R17" t="n">
-        <v>6936707</v>
+        <v>6936737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125568260</v>
+        <v>125569837</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,34 +2302,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603930</v>
+        <v>604041</v>
       </c>
       <c r="R18" t="n">
-        <v>6936683</v>
+        <v>6936707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,15 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125568231</v>
+        <v>125570268</v>
       </c>
       <c r="B19" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,14 +2419,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603930</v>
+        <v>603962</v>
       </c>
       <c r="R19" t="n">
-        <v>6936683</v>
+        <v>6936624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,15 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125570219</v>
+        <v>125568231</v>
       </c>
       <c r="B20" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2586,39 +2496,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604001</v>
+        <v>603930</v>
       </c>
       <c r="R20" t="n">
-        <v>6936685</v>
+        <v>6936683</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125568836</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>125569588</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>125568990</v>
       </c>
       <c r="B5" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125570230</v>
       </c>
       <c r="B11" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1980,45 +1980,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569656</v>
+        <v>125569639</v>
       </c>
       <c r="B15" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604000</v>
+        <v>603993</v>
       </c>
       <c r="R15" t="n">
-        <v>6936712</v>
+        <v>6936737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2056,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,50 +2194,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569639</v>
+        <v>125569656</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603993</v>
+        <v>604000</v>
       </c>
       <c r="R17" t="n">
-        <v>6936737</v>
+        <v>6936712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,11 +2265,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125569837</v>
+        <v>125570268</v>
       </c>
       <c r="B18" t="n">
         <v>80070</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604041</v>
+        <v>603962</v>
       </c>
       <c r="R18" t="n">
-        <v>6936707</v>
+        <v>6936624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125570268</v>
+        <v>125569837</v>
       </c>
       <c r="B19" t="n">
         <v>80070</v>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603962</v>
+        <v>604041</v>
       </c>
       <c r="R19" t="n">
-        <v>6936624</v>
+        <v>6936707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125568260</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125568836</v>
       </c>
       <c r="B3" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569588</v>
+        <v>125569404</v>
       </c>
       <c r="B4" t="n">
-        <v>91227</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,34 +884,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603975</v>
+        <v>603964</v>
       </c>
       <c r="R4" t="n">
-        <v>6936747</v>
+        <v>6936709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125568990</v>
+        <v>125569588</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R5" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569404</v>
+        <v>125568990</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>91228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,29 +1083,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125570230</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1980,50 +1980,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569639</v>
+        <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603993</v>
+        <v>604000</v>
       </c>
       <c r="R15" t="n">
-        <v>6936737</v>
+        <v>6936712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,7 +2077,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570015</v>
+        <v>125569639</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2118,7 +2108,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2127,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604077</v>
+        <v>603993</v>
       </c>
       <c r="R16" t="n">
-        <v>6936714</v>
+        <v>6936737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,45 +2184,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569656</v>
+        <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604000</v>
+        <v>604077</v>
       </c>
       <c r="R17" t="n">
-        <v>6936712</v>
+        <v>6936714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,7 +2294,7 @@
         <v>125570268</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>125569837</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>125568231</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,48 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125568836</v>
+        <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>91193</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R3" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,50 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569404</v>
+        <v>125568836</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R4" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,6 +956,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1980,45 +1980,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569656</v>
+        <v>125569639</v>
       </c>
       <c r="B15" t="n">
-        <v>97212</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604000</v>
+        <v>603993</v>
       </c>
       <c r="R15" t="n">
-        <v>6936712</v>
+        <v>6936737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2056,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2077,7 +2087,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569639</v>
+        <v>125570015</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2108,7 +2118,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2117,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603993</v>
+        <v>604077</v>
       </c>
       <c r="R16" t="n">
-        <v>6936737</v>
+        <v>6936714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,50 +2194,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570015</v>
+        <v>125569656</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604077</v>
+        <v>604000</v>
       </c>
       <c r="R17" t="n">
-        <v>6936714</v>
+        <v>6936712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,11 +2265,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125568260</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569404</v>
+        <v>125569588</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R3" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,48 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568836</v>
+        <v>125568990</v>
       </c>
       <c r="B4" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R4" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,45 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125569588</v>
+        <v>125568836</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603975</v>
+        <v>603952</v>
       </c>
       <c r="R5" t="n">
-        <v>6936747</v>
+        <v>6936705</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125568990</v>
+        <v>125569404</v>
       </c>
       <c r="B6" t="n">
-        <v>91228</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,24 +1078,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125570230</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>125569656</v>
       </c>
       <c r="B17" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>125570268</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>125569837</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>125568231</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570366</v>
+        <v>125569912</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,34 +1277,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603906</v>
+        <v>604067</v>
       </c>
       <c r="R8" t="n">
-        <v>6936672</v>
+        <v>6936731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125569912</v>
+        <v>125570366</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,39 +1384,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604067</v>
+        <v>603906</v>
       </c>
       <c r="R9" t="n">
-        <v>6936731</v>
+        <v>6936672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1444,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569588</v>
+        <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603975</v>
+        <v>603964</v>
       </c>
       <c r="R3" t="n">
-        <v>6936747</v>
+        <v>6936709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568990</v>
+        <v>125568836</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R4" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +956,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,48 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125568836</v>
+        <v>125569588</v>
       </c>
       <c r="B5" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603952</v>
+        <v>603975</v>
       </c>
       <c r="R5" t="n">
-        <v>6936705</v>
+        <v>6936747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,7 +1054,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569404</v>
+        <v>125568990</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,29 +1083,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125569912</v>
+        <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,39 +1277,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604067</v>
+        <v>603906</v>
       </c>
       <c r="R8" t="n">
-        <v>6936731</v>
+        <v>6936672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,11 +1337,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125570366</v>
+        <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,34 +1374,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603906</v>
+        <v>604067</v>
       </c>
       <c r="R9" t="n">
-        <v>6936672</v>
+        <v>6936731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1980,50 +1980,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569639</v>
+        <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603993</v>
+        <v>604000</v>
       </c>
       <c r="R15" t="n">
-        <v>6936737</v>
+        <v>6936712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,7 +2077,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570015</v>
+        <v>125569639</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2118,7 +2108,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2127,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604077</v>
+        <v>603993</v>
       </c>
       <c r="R16" t="n">
-        <v>6936714</v>
+        <v>6936737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,45 +2184,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569656</v>
+        <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>97216</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604000</v>
+        <v>604077</v>
       </c>
       <c r="R17" t="n">
-        <v>6936712</v>
+        <v>6936714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125570268</v>
+        <v>125569837</v>
       </c>
       <c r="B18" t="n">
         <v>80075</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603962</v>
+        <v>604041</v>
       </c>
       <c r="R18" t="n">
-        <v>6936624</v>
+        <v>6936707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125569837</v>
+        <v>125570268</v>
       </c>
       <c r="B19" t="n">
         <v>80075</v>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604041</v>
+        <v>603962</v>
       </c>
       <c r="R19" t="n">
-        <v>6936707</v>
+        <v>6936624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569404</v>
+        <v>125569588</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R3" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,48 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568836</v>
+        <v>125568990</v>
       </c>
       <c r="B4" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R4" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125569588</v>
+        <v>125569404</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603975</v>
+        <v>603964</v>
       </c>
       <c r="R5" t="n">
-        <v>6936747</v>
+        <v>6936709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,45 +1068,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125568990</v>
+        <v>125568836</v>
       </c>
       <c r="B6" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R6" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1150,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1980,45 +1980,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569656</v>
+        <v>125569639</v>
       </c>
       <c r="B15" t="n">
-        <v>97217</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604000</v>
+        <v>603993</v>
       </c>
       <c r="R15" t="n">
-        <v>6936712</v>
+        <v>6936737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2056,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2077,7 +2087,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569639</v>
+        <v>125570015</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2108,7 +2118,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2117,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603993</v>
+        <v>604077</v>
       </c>
       <c r="R16" t="n">
-        <v>6936737</v>
+        <v>6936714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,50 +2194,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570015</v>
+        <v>125569656</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604077</v>
+        <v>604000</v>
       </c>
       <c r="R17" t="n">
-        <v>6936714</v>
+        <v>6936712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,11 +2265,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125568260</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569588</v>
+        <v>125568990</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603975</v>
+        <v>603964</v>
       </c>
       <c r="R3" t="n">
-        <v>6936747</v>
+        <v>6936709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568990</v>
+        <v>125569588</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R4" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,50 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125569404</v>
+        <v>125568836</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>91199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R5" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,48 +1067,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125568836</v>
+        <v>125569404</v>
       </c>
       <c r="B6" t="n">
-        <v>91197</v>
+        <v>57649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R6" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125569123</v>
+        <v>125568069</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,34 +1481,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603952</v>
+        <v>603923</v>
       </c>
       <c r="R10" t="n">
-        <v>6936705</v>
+        <v>6936700</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,6 +1546,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125570230</v>
+        <v>125569123</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603979</v>
+        <v>603952</v>
       </c>
       <c r="R11" t="n">
-        <v>6936633</v>
+        <v>6936705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,10 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125568069</v>
+        <v>125570230</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>91530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,39 +1685,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603923</v>
+        <v>603979</v>
       </c>
       <c r="R12" t="n">
-        <v>6936700</v>
+        <v>6936633</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,11 +1745,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>125566395</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,50 +1980,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569639</v>
+        <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>97219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603993</v>
+        <v>604000</v>
       </c>
       <c r="R15" t="n">
-        <v>6936737</v>
+        <v>6936712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570015</v>
+        <v>125569639</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2118,7 +2108,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2127,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604077</v>
+        <v>603993</v>
       </c>
       <c r="R16" t="n">
-        <v>6936714</v>
+        <v>6936737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,45 +2184,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569656</v>
+        <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>97217</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604000</v>
+        <v>604077</v>
       </c>
       <c r="R17" t="n">
-        <v>6936712</v>
+        <v>6936714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,7 +2294,7 @@
         <v>125569837</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>125570268</v>
       </c>
       <c r="B19" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>125568231</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125568069</v>
+        <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>91530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,39 +1481,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603923</v>
+        <v>603952</v>
       </c>
       <c r="R10" t="n">
-        <v>6936700</v>
+        <v>6936705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,11 +1541,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,7 +1567,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125569123</v>
+        <v>125570230</v>
       </c>
       <c r="B11" t="n">
         <v>91530</v>
@@ -1612,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603952</v>
+        <v>603979</v>
       </c>
       <c r="R11" t="n">
-        <v>6936705</v>
+        <v>6936633</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125570230</v>
+        <v>125568069</v>
       </c>
       <c r="B12" t="n">
-        <v>91530</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,34 +1675,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603979</v>
+        <v>603923</v>
       </c>
       <c r="R12" t="n">
-        <v>6936633</v>
+        <v>6936700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,6 +1740,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125568990</v>
+        <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>91234</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,24 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -869,45 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569588</v>
+        <v>125568836</v>
       </c>
       <c r="B4" t="n">
-        <v>91234</v>
+        <v>91201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603975</v>
+        <v>603952</v>
       </c>
       <c r="R4" t="n">
-        <v>6936747</v>
+        <v>6936705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +956,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,48 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125568836</v>
+        <v>125569588</v>
       </c>
       <c r="B5" t="n">
-        <v>91199</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603952</v>
+        <v>603975</v>
       </c>
       <c r="R5" t="n">
-        <v>6936705</v>
+        <v>6936747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,7 +1054,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569404</v>
+        <v>125568990</v>
       </c>
       <c r="B6" t="n">
-        <v>57649</v>
+        <v>91236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,29 +1083,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570366</v>
+        <v>125569912</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,34 +1277,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603906</v>
+        <v>604067</v>
       </c>
       <c r="R8" t="n">
-        <v>6936672</v>
+        <v>6936731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125569912</v>
+        <v>125570366</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,39 +1384,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604067</v>
+        <v>603906</v>
       </c>
       <c r="R9" t="n">
-        <v>6936731</v>
+        <v>6936672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1444,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,7 +1473,7 @@
         <v>125569123</v>
       </c>
       <c r="B10" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125570230</v>
       </c>
       <c r="B11" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1980,45 +1980,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569656</v>
+        <v>125569639</v>
       </c>
       <c r="B15" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604000</v>
+        <v>603993</v>
       </c>
       <c r="R15" t="n">
-        <v>6936712</v>
+        <v>6936737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2056,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2077,7 +2087,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569639</v>
+        <v>125570015</v>
       </c>
       <c r="B16" t="n">
         <v>57652</v>
@@ -2108,7 +2118,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2117,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603993</v>
+        <v>604077</v>
       </c>
       <c r="R16" t="n">
-        <v>6936737</v>
+        <v>6936714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,50 +2194,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570015</v>
+        <v>125569656</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>97221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604077</v>
+        <v>604000</v>
       </c>
       <c r="R17" t="n">
-        <v>6936714</v>
+        <v>6936712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,11 +2265,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,50 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569404</v>
+        <v>125568836</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>91201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603964</v>
+        <v>603952</v>
       </c>
       <c r="R3" t="n">
-        <v>6936709</v>
+        <v>6936705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568836</v>
+        <v>125569588</v>
       </c>
       <c r="B4" t="n">
-        <v>91201</v>
+        <v>91236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603952</v>
+        <v>603975</v>
       </c>
       <c r="R4" t="n">
-        <v>6936705</v>
+        <v>6936747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,7 +970,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125569588</v>
+        <v>125568990</v>
       </c>
       <c r="B5" t="n">
         <v>91236</v>
@@ -1010,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603975</v>
+        <v>603964</v>
       </c>
       <c r="R5" t="n">
-        <v>6936747</v>
+        <v>6936709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125568990</v>
+        <v>125569404</v>
       </c>
       <c r="B6" t="n">
-        <v>91236</v>
+        <v>57649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,24 +1078,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125569912</v>
+        <v>125570366</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,39 +1277,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604067</v>
+        <v>603906</v>
       </c>
       <c r="R8" t="n">
-        <v>6936731</v>
+        <v>6936672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,11 +1337,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125570366</v>
+        <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,34 +1374,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603906</v>
+        <v>604067</v>
       </c>
       <c r="R9" t="n">
-        <v>6936672</v>
+        <v>6936731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1980,50 +1980,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569639</v>
+        <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>97221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603993</v>
+        <v>604000</v>
       </c>
       <c r="R15" t="n">
-        <v>6936737</v>
+        <v>6936712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,11 +2051,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,7 +2077,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125570015</v>
+        <v>125569639</v>
       </c>
       <c r="B16" t="n">
         <v>57652</v>
@@ -2118,7 +2108,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2127,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604077</v>
+        <v>603993</v>
       </c>
       <c r="R16" t="n">
-        <v>6936714</v>
+        <v>6936737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,45 +2184,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125569656</v>
+        <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>97221</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604000</v>
+        <v>604077</v>
       </c>
       <c r="R17" t="n">
-        <v>6936712</v>
+        <v>6936714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -772,48 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125568836</v>
+        <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>91201</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R3" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125569588</v>
+        <v>125568836</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>91203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603975</v>
+        <v>603952</v>
       </c>
       <c r="R4" t="n">
-        <v>6936747</v>
+        <v>6936705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +956,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -973,7 +978,7 @@
         <v>125568990</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569404</v>
+        <v>125569588</v>
       </c>
       <c r="B6" t="n">
-        <v>57649</v>
+        <v>91238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,39 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R6" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
         <v>125570129</v>
       </c>
       <c r="B7" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125569123</v>
+        <v>125570230</v>
       </c>
       <c r="B10" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603952</v>
+        <v>603979</v>
       </c>
       <c r="R10" t="n">
-        <v>6936705</v>
+        <v>6936633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125570230</v>
+        <v>125569123</v>
       </c>
       <c r="B11" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603979</v>
+        <v>603952</v>
       </c>
       <c r="R11" t="n">
-        <v>6936633</v>
+        <v>6936705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
         <v>125569656</v>
       </c>
       <c r="B15" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125569404</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>125570219</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>125568069</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>125566395</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>125569639</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2580,6 +2580,316 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129925984</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödmyrhamrarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>603930</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6936683</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I grov tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129924530</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80090</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>603962</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6936624</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129926804</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>603969</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6936687</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>125569912</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>125568069</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>125566395</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>125569639</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>125570015</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129925984</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>129924530</v>
       </c>
       <c r="B22" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>129926804</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -2585,7 +2585,7 @@
         <v>129925984</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>129924530</v>
       </c>
       <c r="B22" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>129926804</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125568260</v>
+        <v>125569123</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603930</v>
+        <v>603952</v>
       </c>
       <c r="R2" t="n">
-        <v>6936683</v>
+        <v>6936705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125569404</v>
+        <v>125570230</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603964</v>
+        <v>603979</v>
       </c>
       <c r="R3" t="n">
-        <v>6936709</v>
+        <v>6936633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,48 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125568836</v>
+        <v>125568990</v>
       </c>
       <c r="B4" t="n">
-        <v>91203</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603952</v>
+        <v>603964</v>
       </c>
       <c r="R4" t="n">
-        <v>6936705</v>
+        <v>6936709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125568990</v>
+        <v>125569588</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603964</v>
+        <v>603975</v>
       </c>
       <c r="R5" t="n">
-        <v>6936709</v>
+        <v>6936747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569588</v>
+        <v>125570129</v>
       </c>
       <c r="B6" t="n">
-        <v>91238</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603975</v>
+        <v>604001</v>
       </c>
       <c r="R6" t="n">
-        <v>6936747</v>
+        <v>6936685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,45 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125570129</v>
+        <v>125568836</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604001</v>
+        <v>603952</v>
       </c>
       <c r="R7" t="n">
-        <v>6936685</v>
+        <v>6936705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,6 +1242,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1266,14 +1261,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125570366</v>
+        <v>125568260</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1301,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603906</v>
+        <v>603930</v>
       </c>
       <c r="R8" t="n">
-        <v>6936672</v>
+        <v>6936683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,50 +1358,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125569912</v>
+        <v>125570366</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604067</v>
+        <v>603906</v>
       </c>
       <c r="R9" t="n">
-        <v>6936731</v>
+        <v>6936672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1429,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125570230</v>
+        <v>129924530</v>
       </c>
       <c r="B10" t="n">
-        <v>91534</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603979</v>
+        <v>603962</v>
       </c>
       <c r="R10" t="n">
-        <v>6936633</v>
+        <v>6936624</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,12 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,10 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125569123</v>
+        <v>125568231</v>
       </c>
       <c r="B11" t="n">
-        <v>91534</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,34 +1563,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603952</v>
+        <v>603930</v>
       </c>
       <c r="R11" t="n">
-        <v>6936705</v>
+        <v>6936683</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,10 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125568069</v>
+        <v>125569837</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,39 +1660,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603923</v>
+        <v>604041</v>
       </c>
       <c r="R12" t="n">
-        <v>6936700</v>
+        <v>6936707</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,11 +1720,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1771,10 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125570219</v>
+        <v>125570268</v>
       </c>
       <c r="B13" t="n">
-        <v>57681</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,39 +1757,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604001</v>
+        <v>603962</v>
       </c>
       <c r="R13" t="n">
-        <v>6936685</v>
+        <v>6936624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,27 +1843,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125566395</v>
+        <v>125569404</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1913,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603942</v>
+        <v>603964</v>
       </c>
       <c r="R14" t="n">
-        <v>6936844</v>
+        <v>6936709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,11 +1919,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1980,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125569656</v>
+        <v>125570219</v>
       </c>
       <c r="B15" t="n">
-        <v>97223</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,34 +1956,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604000</v>
+        <v>604001</v>
       </c>
       <c r="R15" t="n">
-        <v>6936712</v>
+        <v>6936685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,27 +2047,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125569639</v>
+        <v>129925984</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2108,19 +2078,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603993</v>
+        <v>603930</v>
       </c>
       <c r="R16" t="n">
-        <v>6936737</v>
+        <v>6936683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2147,17 +2117,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>I grov tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125570015</v>
+        <v>125566159</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604077</v>
+        <v>604069</v>
       </c>
       <c r="R17" t="n">
-        <v>6936714</v>
+        <v>6936885</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125569837</v>
+        <v>125566395</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,34 +2272,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604041</v>
+        <v>603942</v>
       </c>
       <c r="R18" t="n">
-        <v>6936707</v>
+        <v>6936844</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,6 +2337,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125570268</v>
+        <v>125568069</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,34 +2379,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603962</v>
+        <v>603923</v>
       </c>
       <c r="R19" t="n">
-        <v>6936624</v>
+        <v>6936700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2459,6 +2444,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2485,10 +2475,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125568231</v>
+        <v>125569639</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,34 +2486,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603930</v>
+        <v>603993</v>
       </c>
       <c r="R20" t="n">
-        <v>6936683</v>
+        <v>6936737</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129925984</v>
+        <v>125569912</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2613,19 +2613,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603930</v>
+        <v>604067</v>
       </c>
       <c r="R21" t="n">
-        <v>6936683</v>
+        <v>6936731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,17 +2652,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I grov tall</t>
+          <t>Ringhack på tall.  Rinner kåda ur dom övre ringhacken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2689,45 +2689,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129924530</v>
+        <v>125570015</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603962</v>
+        <v>604077</v>
       </c>
       <c r="R22" t="n">
-        <v>6936624</v>
+        <v>6936714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,12 +2759,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2789,7 +2799,7 @@
         <v>129926804</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,6 +2899,103 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125569656</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>604000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6936712</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24424-2025 artfynd.xlsx
+++ b/artfynd/A 24424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125568990</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570129</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125568836</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125568260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570366</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129924530</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125568231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570268</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569404</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570219</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129925984</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566159</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566395</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2472,6 +2562,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125568069</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2579,6 +2674,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569639</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2686,6 +2786,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569912</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570015</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,6 +3009,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926804</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,8 +3111,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>